--- a/patient_falls_data_analysis.xlsx
+++ b/patient_falls_data_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2de5f11d543d1b7d/Documents/GitHub Profile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="519" documentId="8_{1FBDFC85-CF7F-4553-AB6C-9EFC2A744925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49257043-2B8F-410D-8830-423D19461D52}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="8_{1FBDFC85-CF7F-4553-AB6C-9EFC2A744925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D876664D-DBB0-45E5-ABDA-646EF26F35FB}"/>
   <bookViews>
     <workbookView xWindow="10620" yWindow="168" windowWidth="12228" windowHeight="13248" firstSheet="3" activeTab="7" xr2:uid="{B8C31174-D146-46EF-8468-759594012F37}"/>
   </bookViews>
@@ -29,7 +29,7 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1027,14 +1027,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1186,8 +1185,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -8813,37 +8811,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -8890,7 +8857,6 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneSeries val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -17054,11 +17020,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1242060" cy="838200"/>
+    <xdr:ext cx="1242060" cy="1038225"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="10" name="TextBox 9">
@@ -17072,8 +17038,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5372100" y="220980"/>
-          <a:ext cx="1242060" cy="838200"/>
+          <a:off x="5353050" y="123824"/>
+          <a:ext cx="1242060" cy="1038225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17107,11 +17073,11 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Top</a:t>
+            <a:t>Most Common Fall Pattern</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> Fall Pattern:</a:t>
+            <a:t>:</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -17218,8 +17184,8 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>106681</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="unit">
@@ -17242,7 +17208,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -17296,8 +17262,8 @@
       <xdr:row>40</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="13" name="fall_type">
@@ -17320,7 +17286,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -19615,7 +19581,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2877BE1E-5C0D-4214-BB7B-965C0F61EFA4}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2877BE1E-5C0D-4214-BB7B-965C0F61EFA4}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -19854,7 +19820,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2B52CD9-BE48-4E34-A575-EB76E19D28F0}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2B52CD9-BE48-4E34-A575-EB76E19D28F0}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -19941,7 +19907,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D111731C-BCCC-4ADC-9338-4384D569D372}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D111731C-BCCC-4ADC-9338-4384D569D372}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -20031,7 +19997,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{908DD451-AAC6-4E6F-90C6-0603412EA509}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{908DD451-AAC6-4E6F-90C6-0603412EA509}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A3:E9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -20201,7 +20167,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1ACD921-B48D-4C11-B3B2-7E95CB41BE28}" name="PivotTable16" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1ACD921-B48D-4C11-B3B2-7E95CB41BE28}" name="PivotTable16" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -20299,7 +20265,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31825180-C56A-421F-B1BE-882F90A26F21}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31825180-C56A-421F-B1BE-882F90A26F21}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -20451,8 +20417,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="unit" xr10:uid="{6EAF24BA-06A4-43CC-B412-FAFD47BBC18F}" cache="Slicer_unit" caption="unit" rowHeight="247650"/>
-  <slicer name="fall_type" xr10:uid="{9AB357F3-23D8-4E3F-9A4D-ED2F3026BB60}" cache="Slicer_fall_type" caption="fall_type" rowHeight="247650"/>
+  <slicer name="unit" xr10:uid="{6EAF24BA-06A4-43CC-B412-FAFD47BBC18F}" cache="Slicer_unit" caption="Unit" rowHeight="247650"/>
+  <slicer name="fall_type" xr10:uid="{9AB357F3-23D8-4E3F-9A4D-ED2F3026BB60}" cache="Slicer_fall_type" caption="Fall Type" rowHeight="247650"/>
 </slicers>
 </file>
 
@@ -20792,7 +20758,7 @@
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>29</v>
       </c>
     </row>
@@ -20800,7 +20766,7 @@
       <c r="A5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>30</v>
       </c>
     </row>
@@ -20808,7 +20774,7 @@
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>23</v>
       </c>
     </row>
@@ -20816,7 +20782,7 @@
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>38</v>
       </c>
     </row>
@@ -20824,7 +20790,7 @@
       <c r="A8" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>120</v>
       </c>
     </row>
@@ -26563,7 +26529,7 @@
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>92</v>
       </c>
     </row>
@@ -26571,7 +26537,7 @@
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>28</v>
       </c>
     </row>
@@ -26579,7 +26545,7 @@
       <c r="A6" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>120</v>
       </c>
     </row>
@@ -26610,7 +26576,7 @@
       <c r="A4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>14</v>
       </c>
     </row>
@@ -26618,7 +26584,7 @@
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>26</v>
       </c>
     </row>
@@ -26626,7 +26592,7 @@
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>32</v>
       </c>
     </row>
@@ -26634,7 +26600,7 @@
       <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>17</v>
       </c>
     </row>
@@ -26642,7 +26608,7 @@
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>31</v>
       </c>
     </row>
@@ -26650,7 +26616,7 @@
       <c r="A9" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>120</v>
       </c>
     </row>
